--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7403,0.0121,0.0042,0.2233</t>
-  </si>
-  <si>
-    <t>0.0250,0.0008,0.0002,0.9918</t>
-  </si>
-  <si>
-    <t>0.6563,0.0039,0.0017,0.5246</t>
-  </si>
-  <si>
-    <t>0.0078,0.0013,0.0002,0.9972</t>
-  </si>
-  <si>
-    <t>0.9941,0.0010,0.0006,0.0019</t>
-  </si>
-  <si>
-    <t>0.9949,0.0009,0.0003,0.0023</t>
-  </si>
-  <si>
-    <t>0.9912,0.0026,0.0014,0.0019</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9682,0.0287,0.0016,0.0031</t>
-  </si>
-  <si>
-    <t>0.9848,0.0075,0.0016,0.0042</t>
-  </si>
-  <si>
-    <t>0.9962,0.0011,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9924,0.0039,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.9822,0.0025,0.0080,0.0004</t>
-  </si>
-  <si>
-    <t>0.0760,0.0460,0.9143,0.0041</t>
-  </si>
-  <si>
-    <t>0.9518,0.0005,0.0840,0.0001</t>
-  </si>
-  <si>
-    <t>0.0843,0.0086,0.9054,0.0084</t>
-  </si>
-  <si>
-    <t>0.9426,0.0056,0.0233,0.0060</t>
-  </si>
-  <si>
-    <t>0.0029,0.9939,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.0074,0.9832,0.0018,0.0016</t>
-  </si>
-  <si>
-    <t>0.1069,0.8887,0.0094,0.0038</t>
-  </si>
-  <si>
-    <t>0.0223,0.9681,0.0054,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.9977,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9558,0.0007,0.0381,0.0011</t>
-  </si>
-  <si>
-    <t>0.0143,0.0039,0.9688,0.0123</t>
-  </si>
-  <si>
-    <t>0.0035,0.0006,0.9961,0.0002</t>
-  </si>
-  <si>
-    <t>0.1731,0.0091,0.8779,0.0024</t>
-  </si>
-  <si>
-    <t>0.5384,0.0014,0.6110,0.0020</t>
-  </si>
-  <si>
-    <t>0.0256,0.0024,0.9815,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0007,0.9966,0.0011</t>
-  </si>
-  <si>
-    <t>0.8983,0.0991,0.0111,0.0015</t>
-  </si>
-  <si>
-    <t>0.8503,0.1278,0.0364,0.0046</t>
-  </si>
-  <si>
-    <t>0.0008,0.0122,0.9982,0.0005</t>
-  </si>
-  <si>
-    <t>0.0063,0.9525,0.2012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9422,0.0355,0.0192,0.0049</t>
-  </si>
-  <si>
-    <t>0.9517,0.0332,0.0131,0.0038</t>
-  </si>
-  <si>
-    <t>0.9139,0.0815,0.0123,0.0022</t>
-  </si>
-  <si>
-    <t>0.0154,0.9442,0.4301,0.0035</t>
-  </si>
-  <si>
-    <t>0.0248,0.5721,0.1933,0.0477</t>
-  </si>
-  <si>
-    <t>0.1238,0.0145,0.8876,0.0086</t>
-  </si>
-  <si>
-    <t>0.4414,0.0023,0.7341,0.0012</t>
-  </si>
-  <si>
-    <t>0.1196,0.0022,0.8383,0.0176</t>
-  </si>
-  <si>
-    <t>0.0168,0.0347,0.9796,0.0016</t>
-  </si>
-  <si>
-    <t>0.0077,0.9675,0.0159,0.0009</t>
-  </si>
-  <si>
-    <t>0.0005,0.0046,0.9922,0.0134</t>
-  </si>
-  <si>
-    <t>0.0395,0.4373,0.0097,0.8167</t>
-  </si>
-  <si>
-    <t>0.0052,0.9788,0.0297,0.0226</t>
-  </si>
-  <si>
-    <t>0.0449,0.9165,0.0354,0.0081</t>
-  </si>
-  <si>
-    <t>0.0046,0.9788,0.4001,0.0019</t>
-  </si>
-  <si>
-    <t>0.0044,0.0807,0.9830,0.0019</t>
-  </si>
-  <si>
-    <t>0.0052,0.3015,0.9784,0.0003</t>
-  </si>
-  <si>
-    <t>0.0398,0.0074,0.9495,0.0131</t>
-  </si>
-  <si>
-    <t>0.2624,0.0002,0.9237,0.0001</t>
-  </si>
-  <si>
-    <t>0.0168,0.0121,0.9759,0.0047</t>
-  </si>
-  <si>
-    <t>0.0040,0.0230,0.9884,0.0014</t>
-  </si>
-  <si>
-    <t>0.9861,0.0048,0.0037,0.0015</t>
-  </si>
-  <si>
-    <t>0.9477,0.0037,0.0182,0.0166</t>
-  </si>
-  <si>
-    <t>0.9684,0.0020,0.0166,0.0040</t>
-  </si>
-  <si>
-    <t>0.0058,0.1169,0.9825,0.0287</t>
-  </si>
-  <si>
-    <t>0.9917,0.0014,0.0023,0.0016</t>
-  </si>
-  <si>
-    <t>0.9896,0.0031,0.0033,0.0009</t>
-  </si>
-  <si>
-    <t>0.9883,0.0043,0.0024,0.0013</t>
-  </si>
-  <si>
-    <t>0.0008,0.7296,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0068,0.0609,0.9858,0.0031</t>
-  </si>
-  <si>
-    <t>0.0020,0.0037,0.9952,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.9326,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0094,0.9950,0.0010</t>
-  </si>
-  <si>
-    <t>0.0269,0.9680,0.0149,0.0002</t>
-  </si>
-  <si>
-    <t>0.0129,0.9763,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.7091,0.0055,0.4332,0.0023</t>
-  </si>
-  <si>
-    <t>0.5915,0.0815,0.3681,0.0047</t>
-  </si>
-  <si>
-    <t>0.0205,0.0469,0.9716,0.0056</t>
-  </si>
-  <si>
-    <t>0.0017,0.6181,0.9656,0.0009</t>
-  </si>
-  <si>
-    <t>0.0015,0.7061,0.9761,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9960,0.0150,0.0009</t>
-  </si>
-  <si>
-    <t>0.0023,0.9018,0.8286,0.0023</t>
-  </si>
-  <si>
-    <t>0.0074,0.0010,0.0138,0.9912</t>
-  </si>
-  <si>
-    <t>0.0004,0.0132,0.0008,0.9987</t>
-  </si>
-  <si>
-    <t>0.0028,0.0007,0.0004,0.9980</t>
-  </si>
-  <si>
-    <t>0.0022,0.0003,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.0014,0.0008,0.0052,0.9971</t>
-  </si>
-  <si>
-    <t>0.0037,0.0057,0.0026,0.9954</t>
-  </si>
-  <si>
-    <t>0.0016,0.9382,0.8990,0.0004</t>
-  </si>
-  <si>
-    <t>0.0027,0.8260,0.9866,0.0002</t>
-  </si>
-  <si>
-    <t>0.0121,0.5672,0.8432,0.0041</t>
-  </si>
-  <si>
-    <t>0.0081,0.8730,0.7614,0.0016</t>
-  </si>
-  <si>
-    <t>0.0018,0.9670,0.7475,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.7258,0.9368,0.0007</t>
-  </si>
-  <si>
-    <t>0.9950,0.0015,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9828,0.0101,0.0030,0.0024</t>
-  </si>
-  <si>
-    <t>0.9917,0.0026,0.0005,0.0023</t>
-  </si>
-  <si>
-    <t>0.9877,0.0038,0.0016,0.0022</t>
-  </si>
-  <si>
-    <t>0.9792,0.0128,0.0023,0.0042</t>
-  </si>
-  <si>
-    <t>0.9945,0.0015,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9729,0.0230,0.0021,0.0031</t>
-  </si>
-  <si>
-    <t>0.9905,0.0041,0.0013,0.0016</t>
-  </si>
-  <si>
-    <t>0.9960,0.0005,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9934,0.0012,0.0017,0.0009</t>
-  </si>
-  <si>
-    <t>0.9862,0.0080,0.0037,0.0015</t>
-  </si>
-  <si>
-    <t>0.9932,0.0016,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9833,0.0032,0.0050,0.0039</t>
-  </si>
-  <si>
-    <t>0.9961,0.0007,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.0013,0.0004,0.9978,0.0014</t>
-  </si>
-  <si>
-    <t>0.0168,0.0134,0.9814,0.0008</t>
-  </si>
-  <si>
-    <t>0.9730,0.0016,0.0105,0.0022</t>
-  </si>
-  <si>
-    <t>0.0156,0.0141,0.9769,0.0011</t>
-  </si>
-  <si>
-    <t>0.0054,0.9883,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.0095,0.9819,0.0060,0.0017</t>
-  </si>
-  <si>
-    <t>0.0759,0.9294,0.0092,0.0016</t>
-  </si>
-  <si>
-    <t>0.0432,0.9314,0.0580,0.0014</t>
-  </si>
-  <si>
-    <t>0.0005,0.9971,0.0012,0.0022</t>
-  </si>
-  <si>
-    <t>0.0012,0.9965,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.7898,0.3141,0.0052,0.0006</t>
-  </si>
-  <si>
-    <t>0.5930,0.1076,0.3648,0.0562</t>
-  </si>
-  <si>
-    <t>0.8032,0.0056,0.2003,0.0078</t>
-  </si>
-  <si>
-    <t>0.7679,0.0237,0.2176,0.0126</t>
-  </si>
-  <si>
-    <t>0.3844,0.0887,0.4728,0.0133</t>
-  </si>
-  <si>
-    <t>0.1462,0.0698,0.2790,0.6770</t>
-  </si>
-  <si>
-    <t>0.0189,0.9647,0.0616,0.0028</t>
-  </si>
-  <si>
-    <t>0.0034,0.9870,0.0651,0.0029</t>
-  </si>
-  <si>
-    <t>0.0013,0.9956,0.0011,0.0023</t>
-  </si>
-  <si>
-    <t>0.0011,0.9886,0.1063,0.0063</t>
-  </si>
-  <si>
-    <t>0.0176,0.9687,0.0239,0.0035</t>
-  </si>
-  <si>
-    <t>0.5710,0.4186,0.1040,0.0071</t>
-  </si>
-  <si>
-    <t>0.5414,0.5102,0.0210,0.0020</t>
-  </si>
-  <si>
-    <t>0.9847,0.0030,0.0050,0.0019</t>
-  </si>
-  <si>
-    <t>0.9891,0.0004,0.0018,0.0039</t>
-  </si>
-  <si>
-    <t>0.9870,0.0023,0.0013,0.0040</t>
-  </si>
-  <si>
-    <t>0.9950,0.0012,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9929,0.0011,0.0007,0.0028</t>
-  </si>
-  <si>
-    <t>0.9974,0.0003,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9941,0.0021,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.9896,0.0018,0.0013,0.0032</t>
-  </si>
-  <si>
-    <t>0.0007,0.6110,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.3293,0.9836,0.0013</t>
-  </si>
-  <si>
-    <t>0.0119,0.0274,0.9774,0.0009</t>
-  </si>
-  <si>
-    <t>0.0014,0.0133,0.9949,0.0008</t>
-  </si>
-  <si>
-    <t>0.9736,0.0017,0.0142,0.0007</t>
-  </si>
-  <si>
-    <t>0.9422,0.0096,0.0256,0.0029</t>
-  </si>
-  <si>
-    <t>0.3930,0.0014,0.7505,0.0022</t>
-  </si>
-  <si>
-    <t>0.8728,0.0296,0.0678,0.0126</t>
-  </si>
-  <si>
-    <t>0.0491,0.0004,0.0004,0.9880</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0005,0.9999</t>
-  </si>
-  <si>
-    <t>0.0021,0.0008,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.0059,0.0005,0.0004,0.9975</t>
-  </si>
-  <si>
-    <t>0.0016,0.9805,0.7432,0.0005</t>
-  </si>
-  <si>
-    <t>0.9836,0.0049,0.0021,0.0051</t>
-  </si>
-  <si>
-    <t>0.5397,0.4072,0.0200,0.0370</t>
-  </si>
-  <si>
-    <t>0.9761,0.0009,0.0053,0.0066</t>
-  </si>
-  <si>
-    <t>0.5160,0.2594,0.1773,0.0089</t>
-  </si>
-  <si>
-    <t>0.9802,0.0028,0.0039,0.0043</t>
-  </si>
-  <si>
-    <t>0.5866,0.0271,0.0136,0.5043</t>
-  </si>
-  <si>
-    <t>0.9942,0.0007,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.2118,0.9204,0.0841</t>
-  </si>
-  <si>
-    <t>0.7864,0.0005,0.0007,0.4559</t>
-  </si>
-  <si>
-    <t>0.9879,0.0015,0.0018,0.0030</t>
-  </si>
-  <si>
-    <t>0.3076,0.4859,0.1690,0.0413</t>
-  </si>
-  <si>
-    <t>0.9850,0.0064,0.0021,0.0009</t>
-  </si>
-  <si>
-    <t>0.8843,0.0307,0.0881,0.0059</t>
-  </si>
-  <si>
-    <t>0.1225,0.8007,0.0756,0.0418</t>
-  </si>
-  <si>
-    <t>0.8363,0.1072,0.0682,0.0078</t>
-  </si>
-  <si>
-    <t>0.9869,0.0036,0.0036,0.0005</t>
-  </si>
-  <si>
-    <t>0.9804,0.0084,0.0026,0.0042</t>
-  </si>
-  <si>
-    <t>0.9951,0.0016,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9812,0.0020,0.0080,0.0031</t>
-  </si>
-  <si>
-    <t>0.9923,0.0009,0.0014,0.0016</t>
-  </si>
-  <si>
-    <t>0.9871,0.0012,0.0036,0.0016</t>
-  </si>
-  <si>
-    <t>0.9868,0.0098,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9905,0.0028,0.0018,0.0026</t>
-  </si>
-  <si>
-    <t>0.9908,0.0005,0.0006,0.0047</t>
-  </si>
-  <si>
-    <t>0.9702,0.0092,0.0004,0.0047</t>
-  </si>
-  <si>
-    <t>0.8601,0.0917,0.0361,0.0018</t>
-  </si>
-  <si>
-    <t>0.8871,0.1132,0.0155,0.0013</t>
-  </si>
-  <si>
-    <t>0.0194,0.0714,0.9634,0.0090</t>
-  </si>
-  <si>
-    <t>0.9924,0.0047,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9800,0.0122,0.0025,0.0032</t>
-  </si>
-  <si>
-    <t>0.9928,0.0023,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.9915,0.0025,0.0005,0.0018</t>
-  </si>
-  <si>
-    <t>0.0007,0.0055,0.9988,0.0014</t>
-  </si>
-  <si>
-    <t>0.9573,0.0234,0.0103,0.0084</t>
-  </si>
-  <si>
-    <t>0.0073,0.0010,0.9943,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.0029,0.9972,0.0005</t>
-  </si>
-  <si>
-    <t>0.0065,0.0036,0.9896,0.0032</t>
-  </si>
-  <si>
-    <t>0.0019,0.0716,0.9939,0.0005</t>
-  </si>
-  <si>
-    <t>0.0027,0.0167,0.9905,0.0018</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0038,0.9933,0.0017</t>
-  </si>
-  <si>
-    <t>0.3451,0.0021,0.7601,0.0029</t>
-  </si>
-  <si>
-    <t>0.5972,0.0094,0.4684,0.0025</t>
-  </si>
-  <si>
-    <t>0.7220,0.0680,0.2378,0.0125</t>
-  </si>
-  <si>
-    <t>0.4944,0.0572,0.4977,0.0114</t>
-  </si>
-  <si>
-    <t>0.0107,0.1260,0.8978,0.0093</t>
-  </si>
-  <si>
-    <t>0.8232,0.0098,0.2165,0.0011</t>
-  </si>
-  <si>
-    <t>0.7894,0.0185,0.1588,0.0270</t>
-  </si>
-  <si>
-    <t>0.7558,0.0138,0.2298,0.0197</t>
-  </si>
-  <si>
-    <t>0.0798,0.9300,0.0052,0.0008</t>
-  </si>
-  <si>
-    <t>0.3030,0.7507,0.0073,0.0024</t>
-  </si>
-  <si>
-    <t>0.9574,0.0554,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.9535,0.0330,0.0111,0.0094</t>
-  </si>
-  <si>
-    <t>0.7765,0.3440,0.0035,0.0014</t>
-  </si>
-  <si>
-    <t>0.9274,0.0179,0.0324,0.0030</t>
-  </si>
-  <si>
-    <t>0.9327,0.0018,0.0697,0.0012</t>
-  </si>
-  <si>
-    <t>0.9448,0.0015,0.0119,0.0144</t>
-  </si>
-  <si>
-    <t>0.7670,0.0020,0.3014,0.0023</t>
-  </si>
-  <si>
-    <t>0.8367,0.0065,0.1873,0.0058</t>
-  </si>
-  <si>
-    <t>0.0397,0.0047,0.9600,0.0124</t>
-  </si>
-  <si>
-    <t>0.0233,0.6200,0.8621,0.0118</t>
-  </si>
-  <si>
-    <t>0.0452,0.1038,0.9172,0.0039</t>
-  </si>
-  <si>
-    <t>0.1350,0.0090,0.8691,0.0032</t>
-  </si>
-  <si>
-    <t>0.0440,0.1711,0.7124,0.0034</t>
-  </si>
-  <si>
-    <t>0.9818,0.0002,0.0001,0.0246</t>
-  </si>
-  <si>
-    <t>0.9909,0.0010,0.0012,0.0032</t>
-  </si>
-  <si>
-    <t>0.9916,0.0032,0.0007,0.0016</t>
-  </si>
-  <si>
-    <t>0.9869,0.0121,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9811,0.0066,0.0053,0.0033</t>
-  </si>
-  <si>
-    <t>0.9944,0.0010,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9960,0.0003,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.9948,0.0011,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.0011,0.0565,0.9942,0.0031</t>
-  </si>
-  <si>
-    <t>0.0616,0.1957,0.8481,0.0100</t>
-  </si>
-  <si>
-    <t>0.8749,0.0069,0.0687,0.0153</t>
-  </si>
-  <si>
-    <t>0.0029,0.0027,0.9961,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0009,0.9957,0.0020</t>
-  </si>
-  <si>
-    <t>0.0205,0.1842,0.7528,0.0215</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0440,0.0198,0.9296,0.0067</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0207,0.0145,0.9619,0.0035</t>
-  </si>
-  <si>
-    <t>0.0154,0.0081,0.9776,0.0045</t>
-  </si>
-  <si>
-    <t>0.9083,0.0005,0.1022,0.0021</t>
-  </si>
-  <si>
-    <t>0.1307,0.0022,0.8886,0.0078</t>
-  </si>
-  <si>
-    <t>0.9021,0.0048,0.0739,0.0043</t>
-  </si>
-  <si>
-    <t>0.9757,0.0108,0.0031,0.0080</t>
-  </si>
-  <si>
-    <t>0.9904,0.0018,0.0022,0.0017</t>
-  </si>
-  <si>
-    <t>0.9894,0.0015,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.9795,0.0124,0.0041,0.0018</t>
-  </si>
-  <si>
-    <t>0.9922,0.0003,0.0003,0.0070</t>
-  </si>
-  <si>
-    <t>0.9836,0.0035,0.0069,0.0011</t>
-  </si>
-  <si>
-    <t>0.9931,0.0017,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.9823,0.0063,0.0023,0.0067</t>
-  </si>
-  <si>
-    <t>0.0117,0.0162,0.9702,0.0022</t>
-  </si>
-  <si>
-    <t>0.0110,0.0614,0.9837,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.0089,0.9875,0.0028</t>
-  </si>
-  <si>
-    <t>0.0248,0.0320,0.9502,0.0040</t>
-  </si>
-  <si>
-    <t>0.0082,0.0004,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0640,0.0041,0.6143,0.2528</t>
-  </si>
-  <si>
-    <t>0.0683,0.0111,0.9235,0.0133</t>
-  </si>
-  <si>
-    <t>0.3491,0.0412,0.6519,0.0187</t>
-  </si>
-  <si>
-    <t>0.9610,0.0045,0.0035,0.0206</t>
-  </si>
-  <si>
-    <t>0.0203,0.0207,0.0033,0.9835</t>
-  </si>
-  <si>
-    <t>0.0072,0.0053,0.0020,0.9933</t>
-  </si>
-  <si>
-    <t>0.0030,0.0003,0.0007,0.9977</t>
-  </si>
-  <si>
-    <t>0.0037,0.0004,0.0015,0.9965</t>
-  </si>
-  <si>
-    <t>0.9354,0.0092,0.0335,0.0100</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.8032,0.0062,0.0192,0.1475</t>
+  </si>
+  <si>
+    <t>0.0551,0.0008,0.0005,0.9856</t>
+  </si>
+  <si>
+    <t>0.6045,0.0035,0.0006,0.5402</t>
+  </si>
+  <si>
+    <t>0.2354,0.0108,0.0042,0.8744</t>
+  </si>
+  <si>
+    <t>0.9904,0.0031,0.0017,0.0019</t>
+  </si>
+  <si>
+    <t>0.9957,0.0012,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9881,0.0041,0.0033,0.0017</t>
+  </si>
+  <si>
+    <t>0.9961,0.0003,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9814,0.0057,0.0019,0.0066</t>
+  </si>
+  <si>
+    <t>0.9797,0.0061,0.0042,0.0047</t>
+  </si>
+  <si>
+    <t>0.9936,0.0006,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9945,0.0013,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.8935,0.0454,0.0369,0.0028</t>
+  </si>
+  <si>
+    <t>0.0428,0.0077,0.9550,0.0031</t>
+  </si>
+  <si>
+    <t>0.4887,0.0030,0.7160,0.0005</t>
+  </si>
+  <si>
+    <t>0.0050,0.0035,0.9936,0.0012</t>
+  </si>
+  <si>
+    <t>0.8008,0.0100,0.1852,0.0059</t>
+  </si>
+  <si>
+    <t>0.0035,0.9926,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9960,0.0012,0.0053</t>
+  </si>
+  <si>
+    <t>0.2457,0.7500,0.0168,0.0050</t>
+  </si>
+  <si>
+    <t>0.0032,0.9910,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.9985,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9297,0.0014,0.0705,0.0016</t>
+  </si>
+  <si>
+    <t>0.7850,0.0011,0.3123,0.0012</t>
+  </si>
+  <si>
+    <t>0.0071,0.0010,0.9931,0.0004</t>
+  </si>
+  <si>
+    <t>0.0349,0.0023,0.9767,0.0006</t>
+  </si>
+  <si>
+    <t>0.0554,0.0030,0.9767,0.0005</t>
+  </si>
+  <si>
+    <t>0.0788,0.0003,0.9688,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.0010,0.9958,0.0012</t>
+  </si>
+  <si>
+    <t>0.7901,0.2296,0.0186,0.0038</t>
+  </si>
+  <si>
+    <t>0.8007,0.0580,0.1550,0.0070</t>
+  </si>
+  <si>
+    <t>0.0008,0.0074,0.9959,0.0134</t>
+  </si>
+  <si>
+    <t>0.0144,0.9579,0.0250,0.0022</t>
+  </si>
+  <si>
+    <t>0.9077,0.0835,0.0134,0.0119</t>
+  </si>
+  <si>
+    <t>0.8415,0.0175,0.1024,0.0034</t>
+  </si>
+  <si>
+    <t>0.8723,0.1482,0.0089,0.0026</t>
+  </si>
+  <si>
+    <t>0.0021,0.9893,0.2761,0.0013</t>
+  </si>
+  <si>
+    <t>0.0165,0.7928,0.0667,0.0352</t>
+  </si>
+  <si>
+    <t>0.0080,0.0126,0.9750,0.0155</t>
+  </si>
+  <si>
+    <t>0.2228,0.0231,0.8579,0.0017</t>
+  </si>
+  <si>
+    <t>0.2052,0.0028,0.7232,0.0206</t>
+  </si>
+  <si>
+    <t>0.0011,0.4005,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.9693,0.0093,0.0034</t>
+  </si>
+  <si>
+    <t>0.0058,0.0157,0.9890,0.0038</t>
+  </si>
+  <si>
+    <t>0.0208,0.6286,0.0072,0.8486</t>
+  </si>
+  <si>
+    <t>0.0071,0.9806,0.0102,0.0108</t>
+  </si>
+  <si>
+    <t>0.0051,0.9883,0.0134,0.0003</t>
+  </si>
+  <si>
+    <t>0.0071,0.9797,0.0499,0.0025</t>
+  </si>
+  <si>
+    <t>0.0014,0.0136,0.9958,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.1292,0.9917,0.0008</t>
+  </si>
+  <si>
+    <t>0.0174,0.0044,0.9805,0.0012</t>
+  </si>
+  <si>
+    <t>0.1148,0.0002,0.9660,0.0001</t>
+  </si>
+  <si>
+    <t>0.0154,0.0122,0.9855,0.0009</t>
+  </si>
+  <si>
+    <t>0.0033,0.2689,0.9629,0.0013</t>
+  </si>
+  <si>
+    <t>0.9421,0.0737,0.0045,0.0021</t>
+  </si>
+  <si>
+    <t>0.9767,0.0008,0.0055,0.0045</t>
+  </si>
+  <si>
+    <t>0.9758,0.0062,0.0149,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.1019,0.9943,0.0184</t>
+  </si>
+  <si>
+    <t>0.9918,0.0031,0.0007,0.0021</t>
+  </si>
+  <si>
+    <t>0.9944,0.0037,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9956,0.0013,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.0040,0.6643,0.9863,0.0007</t>
+  </si>
+  <si>
+    <t>0.0024,0.0300,0.9907,0.0036</t>
+  </si>
+  <si>
+    <t>0.0060,0.0764,0.9674,0.0033</t>
+  </si>
+  <si>
+    <t>0.0008,0.9071,0.9765,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9989,0.0006</t>
+  </si>
+  <si>
+    <t>0.1071,0.8887,0.0168,0.0005</t>
+  </si>
+  <si>
+    <t>0.0024,0.9937,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.8771,0.0022,0.1989,0.0008</t>
+  </si>
+  <si>
+    <t>0.7902,0.0543,0.2070,0.0070</t>
+  </si>
+  <si>
+    <t>0.0049,0.0221,0.9896,0.0040</t>
+  </si>
+  <si>
+    <t>0.0013,0.9713,0.8315,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.6749,0.9491,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9968,0.0244,0.0024</t>
+  </si>
+  <si>
+    <t>0.0007,0.9863,0.6329,0.0007</t>
+  </si>
+  <si>
+    <t>0.0047,0.0004,0.0035,0.9959</t>
+  </si>
+  <si>
+    <t>0.0005,0.0012,0.0002,0.9994</t>
+  </si>
+  <si>
+    <t>0.0017,0.0006,0.0006,0.9981</t>
+  </si>
+  <si>
+    <t>0.0184,0.0011,0.0006,0.9932</t>
+  </si>
+  <si>
+    <t>0.0029,0.0008,0.0010,0.9975</t>
+  </si>
+  <si>
+    <t>0.0015,0.0006,0.0005,0.9984</t>
+  </si>
+  <si>
+    <t>0.0011,0.9546,0.9345,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.7539,0.9915,0.0001</t>
+  </si>
+  <si>
+    <t>0.0141,0.9002,0.2140,0.0100</t>
+  </si>
+  <si>
+    <t>0.0035,0.9599,0.6044,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.9905,0.2905,0.0002</t>
+  </si>
+  <si>
+    <t>0.0039,0.4744,0.9059,0.0009</t>
+  </si>
+  <si>
+    <t>0.9886,0.0034,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.9925,0.0044,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9838,0.0067,0.0053,0.0012</t>
+  </si>
+  <si>
+    <t>0.9904,0.0020,0.0015,0.0023</t>
+  </si>
+  <si>
+    <t>0.9842,0.0070,0.0027,0.0018</t>
+  </si>
+  <si>
+    <t>0.9917,0.0021,0.0017,0.0012</t>
+  </si>
+  <si>
+    <t>0.9860,0.0052,0.0043,0.0017</t>
+  </si>
+  <si>
+    <t>0.9831,0.0067,0.0053,0.0018</t>
+  </si>
+  <si>
+    <t>0.9937,0.0013,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9954,0.0003,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9948,0.0005,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.9949,0.0002,0.0002,0.0036</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0004,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9899,0.0015,0.0022,0.0033</t>
+  </si>
+  <si>
+    <t>0.9906,0.0012,0.0013,0.0035</t>
+  </si>
+  <si>
+    <t>0.0015,0.0014,0.9947,0.0081</t>
+  </si>
+  <si>
+    <t>0.1448,0.0238,0.8861,0.0031</t>
+  </si>
+  <si>
+    <t>0.9431,0.0010,0.0263,0.0036</t>
+  </si>
+  <si>
+    <t>0.0057,0.0008,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0088,0.9719,0.0025,0.0106</t>
+  </si>
+  <si>
+    <t>0.0843,0.9095,0.0164,0.0031</t>
+  </si>
+  <si>
+    <t>0.0085,0.9813,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.0678,0.9151,0.0217,0.0017</t>
+  </si>
+  <si>
+    <t>0.0067,0.9829,0.0050,0.0027</t>
+  </si>
+  <si>
+    <t>0.0027,0.9925,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.8048,0.2648,0.0095,0.0019</t>
+  </si>
+  <si>
+    <t>0.7484,0.1141,0.1029,0.0320</t>
+  </si>
+  <si>
+    <t>0.2096,0.0096,0.7978,0.0191</t>
+  </si>
+  <si>
+    <t>0.6329,0.0163,0.3867,0.0191</t>
+  </si>
+  <si>
+    <t>0.5384,0.0728,0.3887,0.0086</t>
+  </si>
+  <si>
+    <t>0.0170,0.0971,0.1427,0.9151</t>
+  </si>
+  <si>
+    <t>0.0118,0.9787,0.0154,0.0008</t>
+  </si>
+  <si>
+    <t>0.0082,0.9729,0.1246,0.0039</t>
+  </si>
+  <si>
+    <t>0.0009,0.9950,0.0036,0.0039</t>
+  </si>
+  <si>
+    <t>0.0028,0.9836,0.1586,0.0059</t>
+  </si>
+  <si>
+    <t>0.1338,0.8605,0.0251,0.0015</t>
+  </si>
+  <si>
+    <t>0.7419,0.1492,0.1162,0.0029</t>
+  </si>
+  <si>
+    <t>0.2933,0.7075,0.0424,0.0072</t>
+  </si>
+  <si>
+    <t>0.9925,0.0011,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.9859,0.0012,0.0024,0.0047</t>
+  </si>
+  <si>
+    <t>0.9935,0.0009,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.9936,0.0009,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9842,0.0022,0.0005,0.0088</t>
+  </si>
+  <si>
+    <t>0.9902,0.0017,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.9894,0.0020,0.0016,0.0027</t>
+  </si>
+  <si>
+    <t>0.9958,0.0008,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.5862,0.9894,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.5204,0.9728,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0138,0.9895,0.0024</t>
+  </si>
+  <si>
+    <t>0.0030,0.0298,0.9880,0.0006</t>
+  </si>
+  <si>
+    <t>0.9550,0.0039,0.0191,0.0026</t>
+  </si>
+  <si>
+    <t>0.6040,0.0120,0.3109,0.0319</t>
+  </si>
+  <si>
+    <t>0.2439,0.0012,0.8708,0.0022</t>
+  </si>
+  <si>
+    <t>0.6360,0.0603,0.3206,0.0332</t>
+  </si>
+  <si>
+    <t>0.0270,0.0006,0.0011,0.9900</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0028,0.0005,0.0005,0.9980</t>
+  </si>
+  <si>
+    <t>0.0028,0.0003,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0031,0.7304,0.9258,0.0017</t>
+  </si>
+  <si>
+    <t>0.9898,0.0028,0.0009,0.0030</t>
+  </si>
+  <si>
+    <t>0.0711,0.8895,0.0216,0.0394</t>
+  </si>
+  <si>
+    <t>0.9905,0.0015,0.0024,0.0021</t>
+  </si>
+  <si>
+    <t>0.9066,0.0511,0.0329,0.0058</t>
+  </si>
+  <si>
+    <t>0.9939,0.0006,0.0007,0.0019</t>
+  </si>
+  <si>
+    <t>0.7810,0.0101,0.0022,0.2787</t>
+  </si>
+  <si>
+    <t>0.9945,0.0009,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.3025,0.8263,0.1068</t>
+  </si>
+  <si>
+    <t>0.9882,0.0011,0.0022,0.0027</t>
+  </si>
+  <si>
+    <t>0.9633,0.0055,0.0147,0.0094</t>
+  </si>
+  <si>
+    <t>0.3441,0.6823,0.0155,0.0118</t>
+  </si>
+  <si>
+    <t>0.9521,0.0127,0.0148,0.0065</t>
+  </si>
+  <si>
+    <t>0.9838,0.0022,0.0069,0.0006</t>
+  </si>
+  <si>
+    <t>0.8792,0.0940,0.0268,0.0051</t>
+  </si>
+  <si>
+    <t>0.6928,0.2232,0.1395,0.0237</t>
+  </si>
+  <si>
+    <t>0.9673,0.0176,0.0035,0.0037</t>
+  </si>
+  <si>
+    <t>0.9843,0.0034,0.0041,0.0030</t>
+  </si>
+  <si>
+    <t>0.9893,0.0040,0.0013,0.0033</t>
+  </si>
+  <si>
+    <t>0.9821,0.0062,0.0053,0.0022</t>
+  </si>
+  <si>
+    <t>0.9961,0.0005,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9778,0.0049,0.0046,0.0054</t>
+  </si>
+  <si>
+    <t>0.9764,0.0134,0.0030,0.0045</t>
+  </si>
+  <si>
+    <t>0.9898,0.0013,0.0032,0.0018</t>
+  </si>
+  <si>
+    <t>0.9910,0.0008,0.0009,0.0029</t>
+  </si>
+  <si>
+    <t>0.9133,0.0746,0.0021,0.0045</t>
+  </si>
+  <si>
+    <t>0.4547,0.6034,0.0111,0.0016</t>
+  </si>
+  <si>
+    <t>0.8774,0.0937,0.0376,0.0038</t>
+  </si>
+  <si>
+    <t>0.7081,0.1456,0.2329,0.0415</t>
+  </si>
+  <si>
+    <t>0.9815,0.0090,0.0010,0.0032</t>
+  </si>
+  <si>
+    <t>0.9877,0.0025,0.0009,0.0038</t>
+  </si>
+  <si>
+    <t>0.9834,0.0087,0.0033,0.0014</t>
+  </si>
+  <si>
+    <t>0.9825,0.0046,0.0046,0.0021</t>
+  </si>
+  <si>
+    <t>0.0003,0.0240,0.9990,0.0006</t>
+  </si>
+  <si>
+    <t>0.9826,0.0091,0.0020,0.0021</t>
+  </si>
+  <si>
+    <t>0.0022,0.0005,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.0435,0.9952,0.0011</t>
+  </si>
+  <si>
+    <t>0.0230,0.0025,0.9794,0.0029</t>
+  </si>
+  <si>
+    <t>0.0022,0.0582,0.9946,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.0172,0.9929,0.0032</t>
+  </si>
+  <si>
+    <t>0.0058,0.0010,0.9918,0.0030</t>
+  </si>
+  <si>
+    <t>0.0026,0.0204,0.9907,0.0013</t>
+  </si>
+  <si>
+    <t>0.0812,0.0158,0.9132,0.0109</t>
+  </si>
+  <si>
+    <t>0.2084,0.0040,0.8514,0.0023</t>
+  </si>
+  <si>
+    <t>0.5497,0.0263,0.5199,0.0154</t>
+  </si>
+  <si>
+    <t>0.2875,0.0230,0.7701,0.0006</t>
+  </si>
+  <si>
+    <t>0.1216,0.0333,0.8439,0.0032</t>
+  </si>
+  <si>
+    <t>0.6933,0.0028,0.4498,0.0006</t>
+  </si>
+  <si>
+    <t>0.9318,0.0028,0.0623,0.0018</t>
+  </si>
+  <si>
+    <t>0.3652,0.0420,0.6944,0.0043</t>
+  </si>
+  <si>
+    <t>0.0830,0.9265,0.0020,0.0017</t>
+  </si>
+  <si>
+    <t>0.1006,0.9094,0.0023,0.0028</t>
+  </si>
+  <si>
+    <t>0.9571,0.0491,0.0043,0.0022</t>
+  </si>
+  <si>
+    <t>0.6950,0.3859,0.0178,0.0049</t>
+  </si>
+  <si>
+    <t>0.0096,0.9786,0.0023,0.0079</t>
+  </si>
+  <si>
+    <t>0.9529,0.0103,0.0251,0.0009</t>
+  </si>
+  <si>
+    <t>0.9879,0.0001,0.0081,0.0001</t>
+  </si>
+  <si>
+    <t>0.8794,0.0022,0.0275,0.0363</t>
+  </si>
+  <si>
+    <t>0.3690,0.0092,0.6664,0.0174</t>
+  </si>
+  <si>
+    <t>0.8845,0.0144,0.0765,0.0187</t>
+  </si>
+  <si>
+    <t>0.0796,0.0030,0.9332,0.0078</t>
+  </si>
+  <si>
+    <t>0.1762,0.0232,0.6182,0.1070</t>
+  </si>
+  <si>
+    <t>0.0647,0.0143,0.9442,0.0017</t>
+  </si>
+  <si>
+    <t>0.1848,0.0173,0.8555,0.0015</t>
+  </si>
+  <si>
+    <t>0.0274,0.4147,0.5038,0.0203</t>
+  </si>
+  <si>
+    <t>0.9836,0.0018,0.0013,0.0098</t>
+  </si>
+  <si>
+    <t>0.9924,0.0025,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9845,0.0079,0.0030,0.0034</t>
+  </si>
+  <si>
+    <t>0.9901,0.0036,0.0018,0.0017</t>
+  </si>
+  <si>
+    <t>0.9736,0.0045,0.0144,0.0028</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9901,0.0009,0.0010,0.0047</t>
+  </si>
+  <si>
+    <t>0.9915,0.0029,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.0047,0.0178,0.9893,0.0029</t>
+  </si>
+  <si>
+    <t>0.2649,0.0580,0.7555,0.0283</t>
+  </si>
+  <si>
+    <t>0.9773,0.0037,0.0029,0.0071</t>
+  </si>
+  <si>
+    <t>0.0040,0.0010,0.9953,0.0004</t>
+  </si>
+  <si>
+    <t>0.0027,0.0025,0.9906,0.0036</t>
+  </si>
+  <si>
+    <t>0.0147,0.1294,0.8373,0.0079</t>
+  </si>
+  <si>
+    <t>0.0006,0.0023,0.9989,0.0003</t>
+  </si>
+  <si>
+    <t>0.0517,0.0066,0.9525,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.0013,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0117,0.0172,0.9708,0.0009</t>
+  </si>
+  <si>
+    <t>0.0195,0.0647,0.9465,0.0055</t>
+  </si>
+  <si>
+    <t>0.9086,0.0017,0.0902,0.0024</t>
+  </si>
+  <si>
+    <t>0.5220,0.0110,0.5376,0.0090</t>
+  </si>
+  <si>
+    <t>0.9873,0.0006,0.0045,0.0005</t>
+  </si>
+  <si>
+    <t>0.9866,0.0049,0.0009,0.0039</t>
+  </si>
+  <si>
+    <t>0.9876,0.0043,0.0019,0.0019</t>
+  </si>
+  <si>
+    <t>0.9921,0.0025,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.9892,0.0066,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9704,0.0055,0.0036,0.0180</t>
+  </si>
+  <si>
+    <t>0.9860,0.0032,0.0043,0.0016</t>
+  </si>
+  <si>
+    <t>0.9919,0.0042,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9840,0.0033,0.0013,0.0092</t>
+  </si>
+  <si>
+    <t>0.0086,0.0118,0.9787,0.0007</t>
+  </si>
+  <si>
+    <t>0.0031,0.0198,0.9949,0.0004</t>
+  </si>
+  <si>
+    <t>0.0347,0.0073,0.9507,0.0055</t>
+  </si>
+  <si>
+    <t>0.0267,0.0101,0.9624,0.0012</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.3022,0.0087,0.4568,0.1032</t>
+  </si>
+  <si>
+    <t>0.0188,0.0061,0.9701,0.0105</t>
+  </si>
+  <si>
+    <t>0.3643,0.0095,0.3593,0.0877</t>
+  </si>
+  <si>
+    <t>0.9192,0.0031,0.0185,0.0291</t>
+  </si>
+  <si>
+    <t>0.0120,0.0187,0.0009,0.9899</t>
+  </si>
+  <si>
+    <t>0.0169,0.0027,0.0013,0.9891</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0011,0.9992</t>
+  </si>
+  <si>
+    <t>0.0033,0.0005,0.0004,0.9981</t>
+  </si>
+  <si>
+    <t>0.9451,0.0027,0.0288,0.0082</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1978,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2146,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2272,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2566,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3140,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3154,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3560,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3840,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4022,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4078,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4148,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4190,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4358,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4386,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4596,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4610,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4624,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4750,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4848,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5184,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5422,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
